--- a/artfynd/A 20247-2025 artfynd.xlsx
+++ b/artfynd/A 20247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825247</v>
+        <v>124825248</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493777</v>
+        <v>493734</v>
       </c>
       <c r="R2" t="n">
-        <v>6840182</v>
+        <v>6840030</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825248</v>
+        <v>124825247</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493734</v>
+        <v>493777</v>
       </c>
       <c r="R3" t="n">
-        <v>6840030</v>
+        <v>6840182</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 20247-2025 artfynd.xlsx
+++ b/artfynd/A 20247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825248</v>
+        <v>124825247</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493734</v>
+        <v>493777</v>
       </c>
       <c r="R2" t="n">
-        <v>6840030</v>
+        <v>6840182</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825247</v>
+        <v>124825248</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493777</v>
+        <v>493734</v>
       </c>
       <c r="R3" t="n">
-        <v>6840182</v>
+        <v>6840030</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 20247-2025 artfynd.xlsx
+++ b/artfynd/A 20247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825247</v>
+        <v>124825248</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493777</v>
+        <v>493734</v>
       </c>
       <c r="R2" t="n">
-        <v>6840182</v>
+        <v>6840030</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825248</v>
+        <v>124825247</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493734</v>
+        <v>493777</v>
       </c>
       <c r="R3" t="n">
-        <v>6840030</v>
+        <v>6840182</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
